--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260826.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260826.xlsx
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,009,822</t>
+          <t>814,897</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>814,897</t>
+          <t>1,009,822</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,847,000</t>
+          <t>5,767,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,767,000</t>
+          <t>1,847,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>202609WVHFU6F</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>94,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>202609WVHFU6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>94,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>229,000</t>
+          <t>1,572,400</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>1,572,400</t>
+          <t>322,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>322,000</t>
+          <t>229,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>158,000</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>158,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>172,000</t>
+          <t>685,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>179,000</t>
+          <t>256,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>256,000</t>
+          <t>172,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>685,000</t>
+          <t>179,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>116,000</t>
+          <t>72,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>72,000</t>
+          <t>338,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2207,17 +2207,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>338,000</t>
+          <t>116,000</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
